--- a/data/processed/resultado.xlsx
+++ b/data/processed/resultado.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="resultado" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'resultado'!$A$1:$J$108</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -29,12 +31,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,54 +438,66 @@
   </sheetPr>
   <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>consulta_logradouro</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>consulta_numero</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>consulta_bairro</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>consulta_cep</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>consulta_complemento</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>consulta_municipio</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>setor_censitario_encontrado</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>match_status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>match_layer</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>match_score</t>
         </is>
@@ -486,7 +509,6 @@
           <t>RODOVIA BR 101</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>BR101</t>
@@ -545,7 +567,6 @@
           <t>46830000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>290130</t>
@@ -574,8 +595,6 @@
           <t>FAZENDA BICO</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>46130000</t>
@@ -629,7 +648,6 @@
           <t>45675000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>290240</t>
@@ -673,7 +691,6 @@
           <t>47800020</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>290320</t>
@@ -717,7 +734,6 @@
           <t>45860000</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>290630</t>
@@ -746,8 +762,6 @@
           <t>FAZENDA LAGOA GRANDE</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>46380000</t>
@@ -839,13 +853,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>48110000</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>290750</t>
@@ -879,13 +891,11 @@
           <t>89</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>45822000</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>291072</t>
@@ -929,7 +939,6 @@
           <t>44010231</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>291080</t>
@@ -963,7 +972,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>44350000</t>
@@ -1017,7 +1025,6 @@
           <t>46430000</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>291170</t>
@@ -1099,13 +1106,11 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>45745000</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>291210</t>
@@ -1245,7 +1250,6 @@
           <t>45607000</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>291480</t>
@@ -1289,7 +1293,6 @@
           <t>45836000</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>291560</t>
@@ -1371,13 +1374,11 @@
           <t>389</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>45780000</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>291680</t>
@@ -1421,7 +1422,6 @@
           <t>48960000</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>291770</t>
@@ -1455,13 +1455,11 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>48905000</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>291840</t>
@@ -1505,7 +1503,6 @@
           <t>45490000</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>291880</t>
@@ -1549,7 +1546,6 @@
           <t>45490000</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>291880</t>
@@ -1593,7 +1589,6 @@
           <t>48720000</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>291910</t>
@@ -1685,7 +1680,6 @@
           <t>45255000</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>292145</t>
@@ -1729,7 +1723,6 @@
           <t>45890000</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>292390</t>
@@ -1773,7 +1766,6 @@
           <t>47240000</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>292440</t>
@@ -1807,13 +1799,11 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>48120000</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>292520</t>
@@ -1857,7 +1847,6 @@
           <t>45810000</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>292530</t>
@@ -1891,13 +1880,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>45816000</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>292530</t>
@@ -1931,13 +1918,11 @@
           <t>508</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>45810000</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>292530</t>
@@ -1981,7 +1966,6 @@
           <t>45810000</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>292530</t>
@@ -2025,7 +2009,6 @@
           <t>48860000</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>292580</t>
@@ -2117,7 +2100,6 @@
           <t>40750670</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>292740</t>
@@ -2161,7 +2143,6 @@
           <t>41190000</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>292740</t>
@@ -2205,7 +2186,6 @@
           <t>41925540</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>292740</t>
@@ -2249,7 +2229,6 @@
           <t>41290001</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>292740</t>
@@ -2283,13 +2262,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>40470380</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>292740</t>
@@ -2323,13 +2300,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>40370330</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>292740</t>
@@ -2363,7 +2338,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>40820060</t>
@@ -2417,7 +2391,6 @@
           <t>44190000</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>292880</t>
@@ -2446,8 +2419,6 @@
           <t>SITIO ESPERANCA</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>48895000</t>
@@ -2501,7 +2472,6 @@
           <t>48700000</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>293050</t>
@@ -2545,7 +2515,6 @@
           <t>48925000</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>293077</t>
@@ -2589,7 +2558,6 @@
           <t>45998000</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>293135</t>
@@ -2618,7 +2586,6 @@
           <t>FAZENDA QUEIMADA DOS PADEIROS</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>QUEIMADAS DOS LOIOLAS</t>
@@ -2677,7 +2644,6 @@
           <t>45545000</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>293220</t>
@@ -2721,7 +2687,6 @@
           <t>45690000</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>293250</t>
@@ -2765,7 +2730,6 @@
           <t>44470000</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>293320</t>
@@ -2809,7 +2773,6 @@
           <t>47400000</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>293360</t>
@@ -2838,8 +2801,6 @@
           <t>AVENIDA CALDEIRO DA VACA</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>48990000</t>
@@ -2893,7 +2854,6 @@
           <t>44620000</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>290260</t>
@@ -2937,7 +2897,6 @@
           <t>47800200</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>290320</t>
@@ -3029,7 +2988,6 @@
           <t>45800000</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>290340</t>
@@ -3063,13 +3021,11 @@
           <t>68</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>47600000</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>290390</t>
@@ -3098,7 +3054,6 @@
           <t>RUA AMAZONAS</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>MALEMBA DE BAIXO</t>
@@ -3243,7 +3198,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>44500000</t>
@@ -3287,13 +3241,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>48730000</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>290840</t>
@@ -3375,13 +3327,11 @@
           <t>315</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>48480000</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>290960</t>
@@ -3463,13 +3413,11 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>45840000</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>291180</t>
@@ -3498,8 +3446,6 @@
           <t>RUA SANTA ISABEL</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>46860000</t>
@@ -3553,7 +3499,6 @@
           <t>45570000</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>291390</t>
@@ -3597,7 +3542,6 @@
           <t>44900000</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>291460</t>
@@ -3641,7 +3585,6 @@
           <t>45607000</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>291480</t>
@@ -3675,13 +3618,11 @@
           <t>103</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>45455000</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>291570</t>
@@ -3725,7 +3666,6 @@
           <t>44460000</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>291610</t>
@@ -3759,13 +3699,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>45350000</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>291690</t>
@@ -3809,7 +3747,6 @@
           <t>44700000</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>291750</t>
@@ -3853,7 +3790,6 @@
           <t>45206000</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>291800</t>
@@ -3887,7 +3823,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>48905000</t>
@@ -3926,8 +3861,6 @@
           <t>RUA JULIO VERNE</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>47850000</t>
@@ -3971,13 +3904,11 @@
           <t>250</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>44575000</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>292220</t>
@@ -4069,7 +4000,6 @@
           <t>48870000</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>292265</t>
@@ -4242,8 +4172,6 @@
           <t>RUA ADEGUNDES ARAUJO</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>45890000</t>
@@ -4287,13 +4215,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>44830000</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>292480</t>
@@ -4337,7 +4263,6 @@
           <t>45190000</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>292500</t>
@@ -4462,8 +4387,6 @@
           <t>AVENIDA LEOVIGILDO FILGUEIRAS</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>40421020</t>
@@ -4565,7 +4488,6 @@
           <t>41400000</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>292740</t>
@@ -4599,7 +4521,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>41340295</t>
@@ -4691,7 +4612,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>40735560</t>
@@ -4735,7 +4655,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>41611685</t>
@@ -4827,13 +4746,11 @@
           <t>33</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>44571050</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>292870</t>
@@ -4877,7 +4794,6 @@
           <t>44190000</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>292880</t>
@@ -4921,7 +4837,6 @@
           <t>44550000</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>292910</t>
@@ -4965,7 +4880,6 @@
           <t>44915000</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>292925</t>
@@ -5009,7 +4923,6 @@
           <t>43850000</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>292950</t>
@@ -5091,13 +5004,11 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>47630000</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>293015</t>
@@ -5141,7 +5052,6 @@
           <t>44270000</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>293170</t>
@@ -5165,6 +5075,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/processed/resultado.xlsx
+++ b/data/processed/resultado.xlsx
@@ -31,7 +31,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8F0D8"/>
+        <bgColor rgb="00D8F0D8"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -71,6 +83,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,4573 +518,4686 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>RODOVIA BR 101</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>BR101</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>48030260</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>290070</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>290070205000118P</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>38.23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>RUA RIO BAIANO</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>CENTRO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>46830000</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>290130</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>290130405000006P</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4" t="n">
         <v>25.39</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>FAZENDA BICO</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>46130000</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>290200</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>290200505000039P</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="n">
         <v>20.85</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>DISTRITO 2 DE JULHO</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>POCO CENTRAL</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>45675000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>290240</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>290240105000018P</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>22.41</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>RUA SERGIO BOMFIM</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>BARREIRINHAS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>47800020</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>290320</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>290320105000053P</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="4" t="n">
         <v>16.44</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>None EVILASIO FIRMATO</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>SOCRATES REZENDE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>45860000</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>290630</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>290630305000025P</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>25.85</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>FAZENDA LAGOA GRANDE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>46380000</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>290660</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>290660005000007P</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="n">
         <v>25.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CONJUNTO URBES NOVA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>NOVA PASTORA</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>48390000</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>290700</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>290700405000002P</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>30.58</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CONDOMINIO RESI DOUTOR ANTONIO CARLOS GOES</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>48110000</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>290750</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>290750905000085P</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="n">
         <v>29.24</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>RUA CASSIMIRO DE ABREU</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>45822000</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>291072</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>291072705000208P</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3" t="n">
         <v>16.33</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>AVENIDA SENHOR DOS PASSOS</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>CENTRO</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>44010231</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>291080</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>291080005080001P</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>37.7</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>RUA PADRE PEDRO PEREIRA PROJETO II</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>44350000</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>COELBA</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>291160</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>291160005000025P</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="n">
         <v>28.04</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>RUA JOAQUIM LIMA</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>ALTO CAICARA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>46430000</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>291170</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>291170912000007P</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="I14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>22.92</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>FAZENDA BOA VISTA</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>SAO JOAO DO SUL</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>45840000</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>PROX</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>291180</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>291180805000022P</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="I15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>25.16</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>RUA NOVA</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>45745000</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>291210</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>291210305000047P</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="I16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>18.84</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>RUA DA GAMELEIRA</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>BAIRRO NOVO</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>46770000</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>291430</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>291430705000006P</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="I17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="n">
         <v>22.51</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>FAZENDA PALMEIRAS DO RIACHO</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>ZONA RURAL</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>46770000</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>CASA</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>291430</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>291430710000009P</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4" t="n">
         <v>25.72</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>AVENIDA PRINCESA ISABEL</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>788</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>SAO CAETANO</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>45607000</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>291480</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>291480205000121P</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="3" t="n">
         <v>39.1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>RUA CAMINHO 20 CASA</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>URBIS III</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>45836000</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>291560</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>291560105000150P</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4" t="n">
         <v>29.93</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>FAZENDA PERSEVERANCA</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>CURVELO DA CONCEICAO</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>45970000</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>CASA</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>291600</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>291600515000011P</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4" t="n">
         <v>16.92</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>RUA MACARANI</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>389</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>45780000</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>291680</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>291680705000031P</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>22.48</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>RUA CATUABINHA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>ZONA RURAL</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>48960000</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>291770</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>291770605000013P</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>RUA SENHOR DO BOMFIM</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>48905000</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>291840</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>291840705000178P</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="3" t="n">
         <v>29.38</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>RUA ENTROCAMENTO DE LAJE</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>ZONA RURAL</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>45490000</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>291880</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>291880315000016P</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="n">
         <v>20.74</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>DISTRITO ENG PONTES</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>BELA VITA</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>45490000</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>291880</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>291880315000014P</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4" t="n">
         <v>19.03</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>FAZENDA CATANA NOVO</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>ZONA RURAL</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>48720000</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>291910</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>291910805000004P</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4" t="n">
         <v>24.62</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>RUA BOM JESUS DA LAPA</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>SANTA CRUZ</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>47850000</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>QD 92 L 03</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>291955</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>291955305000082P</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="3" t="n">
         <v>41.4</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>RUA ELVIRA EPFANIA</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>CENTRO</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>45255000</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>292145</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>292145005000001P</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4" t="n">
         <v>31.95</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>RUA JUVINIANO PRUDENTE</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>CENTRO</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>45890000</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>292390</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>292390205000004P</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="I30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>20.63</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>None FAZENDA ESPINHEIRO</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>MANDARINO</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>47240000</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>292440</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>292440515000003P</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="4" t="n">
         <v>22.8</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>RUA ALZIRO ROCHA</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>48120000</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>292520</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>292520405000028P</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4" t="n">
         <v>20.65</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>RUA ALDEIA INDIGENA PATAXO ALDEIA VELHA</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>ARRAIAL DAJUDA</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>45810000</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>292530</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>292530305000191P</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="4" t="n">
         <v>22.16</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>RUA ALFREDO VEIGA</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>45816000</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>292530</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>292530307000009P</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="I34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="n">
         <v>16.34</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>RUA ANTONIA VALADARES</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>45810000</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>292530</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>292530305000153P</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>18.31</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>RUA MARIA ANDRADE</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>UBALDINAO</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>45810000</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>292530</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>292530305000112P</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="4" t="n">
         <v>18.71</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>FAZENDA MACAMBIRO</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>ZONA RURAL</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>48860000</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>292580</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>292580805000018P</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="I37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="n">
         <v>24.04</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>RUA DO PARAISO</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>PARALELA</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>41730140</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>292740805220801P</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="4" t="n">
         <v>21.5</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>RUA SANTO INACIO</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>SANTO INACIO</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>40750670</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>292740805130011P</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4" t="n">
         <v>28.53</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>RUA 30 DE NOVEMBRO</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>SAO GONCALO</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>41190000</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>292740805220789P</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="3" t="n">
         <v>22.69</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>RUA ANTONIO CASAES</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>321</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>CHAPADA DO RIO VERMELHO</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>41925540</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>292740805060046P</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="4" t="n">
         <v>14.39</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>CONJUNTO RESIDE PIRAJA</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>PIRAJA</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>41290001</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>292740805180401P</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" s="4" t="n">
         <v>24.23</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>CONJUNTO JOANE LESTE</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>40470380</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>292740805150141P</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="4" t="n">
         <v>19.86</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>RUA AZEREDO COUTINHO</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>40370330</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>292740805210172P</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="4" t="n">
         <v>28.2</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>RUA VINTE UM DE ABRIL</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>40820060</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>292740805130109P</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="4" t="n">
         <v>15.42</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>AVENIDA JOAO CARVALHO LEITE</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>370</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>CENTRO</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>44190000</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>292880</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>292880205000067P</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="I46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="n">
         <v>22.5</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>SITIO ESPERANCA</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>48895000</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>292895</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>292895005000005P</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="4" t="n">
         <v>21.06</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>PONTA QUEIMADAS</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>RURAL</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>48700000</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>293050</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>293050105000113P</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="4" t="n">
         <v>18.05</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>RUA QD S15 RUA 07 N09</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>VILA SAO JOAQUIM</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>48925000</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>293077</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>293077405000045P</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="4" t="n">
         <v>28.57</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>RUA JABORANDI</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>446</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>LIBERDADE II</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>45998000</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>293135</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>293135010000014P</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="4" t="n">
         <v>22.53</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>FAZENDA QUEIMADA DOS PADEIROS</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>QUEIMADAS DOS LOIOLAS</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>48950000</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>293200</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>293200205000010P</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="4" t="n">
         <v>28.05</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>RUA 2 DE JULHO</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>PIRAUNA</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>45545000</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>293220</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>293220005000016P</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="n">
+      <c r="I52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="3" t="n">
         <v>22.07</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>RUA SAO JORGE</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>OUTEIRO</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>45690000</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>293250</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>293250725000002P</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="I53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="3" t="n">
         <v>21.2</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>RUA NOVA BRASILEIA</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>CACHA PREGOD</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>44470000</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>293320</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>293320810000001P</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="n">
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="4" t="n">
         <v>26.56</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>RUA 51</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>CONJUNTO HABITACIONAL RAUL BRAGA</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>47400000</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>293360</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>293360405000027P</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="4" t="n">
         <v>24.43</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>AVENIDA CALDEIRO DA VACA</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr"/>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>48990000</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>290135</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>290135305000024P</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="4" t="n">
         <v>27.35</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>RUA ADELINO SUZART PEREIRA</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>CENTRO</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>44620000</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>290260</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>290260905000007P</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" t="n">
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="4" t="n">
         <v>33.65</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>RUA F</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>BARAUNA</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>47800200</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>290320</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>290320105000053P</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" s="4" t="n">
         <v>15.67</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>RUA VANDELINO MATOS</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>BARRO ALTO</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>44895000</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>CASA</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>290323</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>290323505000020P</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" t="n">
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="4" t="n">
         <v>20.9</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>TRAVESSA BURANHEN</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>BARROLANDIA</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>45800000</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>290340</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>290340905000006P</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="I60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="n">
         <v>21.44</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>RUA FLUMINENSE</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>47600000</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>290390</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>290390405000020P</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="I61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="n">
         <v>17.98</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>RUA AMAZONAS</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr"/>
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>MALEMBA DE BAIXO</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>43825430</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>290650</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>290650105000017P</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" t="n">
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="4" t="n">
         <v>17.43</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>SITIO LAGOAS NOVAS</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>JARDIM</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>47300000</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>290720</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>290720215000010P</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" t="n">
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="4" t="n">
         <v>24.65</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>FAZENDA RIACHO DA LEGUA</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>ZONA RURAL</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>44500000</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>CASA</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>290730</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>290730125000019P</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="4" t="n">
         <v>31.95</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>TRAVESSA LINHA</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>44500000</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>CASA</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>290730</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>290730105000010P</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" t="n">
+      <c r="I65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="3" t="n">
         <v>20.5</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>RUA MANOEL ALVES SAMPAIO</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>48730000</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>290840</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>290840805000002P</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" t="n">
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="4" t="n">
         <v>30.64</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>DISTRITO TAGUA</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>TAGUA</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>47900000</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>COELBA</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>290940</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>290940615000004P</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" s="4" t="n">
         <v>26.04</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>SITIO PECUARIA</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>48480000</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>290960</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>290960405000014P</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J68" s="4" t="n">
         <v>25.23</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>AVENIDA VINTE E TRES DEABRIL</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>CENTRO</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>45740000</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>CASA</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>291100</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>291100605000006P</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" t="n">
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="4" t="n">
         <v>27.12</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>RUA JOANA MOURA</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>45840000</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>291180</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>291180805000036P</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="4" t="n">
         <v>27.44</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>RUA SANTA ISABEL</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr"/>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>46860000</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>291190</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>291190705000034P</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" t="n">
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="4" t="n">
         <v>24.36</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>RUA 2 DE DEZEMBRO</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>DOIS DE DEZEMBRO</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>45570000</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>291390</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>291390305000002P</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" t="n">
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="4" t="n">
         <v>24.99</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>RUA C 14</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>PARAISO</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>44900000</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>291460</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>291460405000086P</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" t="n">
+      <c r="I73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="3" t="n">
         <v>24.52</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>RUA DA BANANEIRA</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>LOMANTO</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>45607000</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>291480</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>291480205000308P</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" s="4" t="n">
         <v>15.29</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>RUA CRUZEIRO</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr"/>
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>45455000</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>291570</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>291570005000015P</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" s="4" t="n">
         <v>22.13</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>RUA DO CREBRA MAR</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>BOM DESPACHO</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>44460000</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>291610</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>291610405000062P</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" t="n">
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="4" t="n">
         <v>25.83</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>RUA GALDINO OLIVEIRA</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>45350000</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>291690</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>291690605000003P</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" t="n">
+      <c r="I77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="3" t="n">
         <v>21.05</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>RUA DO CAJUEIRO</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>CAIXA DAGUA</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>44700000</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>291750</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>291750805000105P</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" t="n">
+      <c r="I78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="n">
         <v>21.72</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>AVENIDA AMERICANO DA COSTA</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>JOAQUIM ROMAO</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>45206000</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>291800</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>291800105000100P</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" s="4" t="n">
         <v>44.2</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>RUA E</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>48905000</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>CAMINHO 9</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>291840</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>291840705000209P</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J80" s="4" t="n">
         <v>17.26</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>RUA JULIO VERNE</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr"/>
+      <c r="C81" s="4" t="inlineStr"/>
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>47850000</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>QD 7 LT 16</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>291955</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>291955305000191P</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J81" s="4" t="n">
         <v>17.89</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>RUA SAO BENEDITO</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr"/>
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>44575000</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>292220</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>292220110000001P</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J82" s="4" t="n">
         <v>26.34</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>FAZENDA PE DE SERRA</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>ZONA RURAL</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>45480000</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>PROX MARIA SAO</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>292240</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>292240905000035P</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" t="n">
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="4" t="n">
         <v>28.18</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>FAZENDA COSTA</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>JACU</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>48870000</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>292265</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>292265605000022P</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J84" s="4" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>RUA ARCO VERDE</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>CLERISTON ANDRADE</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>45920000</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>SEDE</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>292300</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>292300105000026P</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" t="n">
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="4" t="n">
         <v>34.21</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>10R FAZENDA BOA ESPERANCA</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>RURAL</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>45928000</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>KM 87</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>292300</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>292300110000005P</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" t="n">
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="4" t="n">
         <v>25.38</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>COMUNIDADE ROCA NOVA</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>996</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>ROCA NOVA</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>48430000</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>COELBA</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>292380</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>292380305000020P</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" t="n">
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="4" t="n">
         <v>29.3</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>RUA ADEGUNDES ARAUJO</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr"/>
+      <c r="C88" s="4" t="inlineStr"/>
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>45890000</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>SEM NUMERO</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>292390</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>292390205000005P</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" t="n">
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="4" t="n">
         <v>29.48</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>PRACA DA MATRIZ</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>44830000</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>292480</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>292480125000006P</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" t="n">
+      <c r="I89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="3" t="n">
         <v>23.2</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>RUA ILHEUS</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>MORADA DO PLANALTO</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>45190000</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>292500</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>292500605000022P</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" t="n">
+      <c r="I90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="3" t="n">
         <v>18.86</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>RUA DA EXPANSAO CAIXA D AGUA</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>FRENTE SEMITERIO</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>48630000</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>QD 09 LOTE 07</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>292710</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="4" t="inlineStr">
         <is>
           <t>292710105000040P</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" t="n">
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="4" t="n">
         <v>27.8</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>FAZENDA LAGE</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>PROX SERRA 1</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>46800000</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>CASA</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>292720</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>292720005000062P</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" t="n">
+      <c r="I92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="3" t="n">
         <v>15.73</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>AVENIDA LEOVIGILDO FILGUEIRAS</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr"/>
+      <c r="C93" s="4" t="inlineStr"/>
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>40421020</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>292740805270382P</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J93" s="4" t="n">
         <v>43.97</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>RUA 30</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>CASTELOBRANCO</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>41315000</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>1 ETAPA</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>292740805180068P</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" t="n">
+      <c r="I94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="3" t="n">
         <v>12.79</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>VIA PARAFUSO</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>102E</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>CEASA</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>41400000</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t>292740805070131P</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J95" s="4" t="n">
         <v>24.89</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>LOTEAMENTO DEMOCRATA</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>41340295</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>RUA B</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>292740805220625P</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I96" t="n">
+      <c r="I96" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" s="3" t="n">
         <v>24.22</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>TRAVESSA SANTA MONICA RUA PAULO COSTA</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>CAJAZEIRAS VIII</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>41330020</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>DAS MANGABEIRAS</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>292740805260166P</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" s="4" t="n">
         <v>45.98</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>RUA DEMOSTENES NASCIMENTO</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr"/>
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>40735560</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>292740805160032P</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J98" t="n">
+      <c r="J98" s="4" t="n">
         <v>28.95</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>RUA PRESIDENTE VARGAS</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>41611685</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>292740</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>292740805090293P</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" t="n">
+      <c r="I99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="3" t="n">
         <v>29.47</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>RUA 21 DE JANEIRO</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>CENTRO</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>45320000</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>CASA</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>292790</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>292790305000006P</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" t="n">
+      <c r="I100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="3" t="n">
         <v>27.49</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>RUA DA INDEPENDENCIA</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr"/>
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>44571050</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>292870</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>292870305000110P</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J101" t="n">
+      <c r="J101" s="4" t="n">
         <v>26.72</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>RUA A</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>CAMINHO DO OESTE</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>44190000</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr"/>
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>292880</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>292880205000098P</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" t="n">
+      <c r="I102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="n">
         <v>20.92</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>RUA FAZ RIO DA VARA</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>SAO FELIPE</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>44550000</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>292910</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>292910705000017P</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" t="n">
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="4" t="n">
         <v>19.48</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>RUA SEM DENOMINACAO</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>POVOADO DE JACAREZINHO</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>44915000</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>292925</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>292925515000015P</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H104" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" t="n">
+      <c r="I104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="n">
         <v>25.99</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>RUA NOVA</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>NAZARE DE JACUIPE</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>43850000</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr"/>
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>292950</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G105" s="3" t="inlineStr">
         <is>
           <t>292950305000050P</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" t="n">
+      <c r="I105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="n">
         <v>18.86</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>EIXO ESTRADA VICINAL 01</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>AGROVILA 07</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="4" t="inlineStr">
         <is>
           <t>47630000</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>293015</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>293015405000040P</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>encontrado</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" t="n">
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>encontrado</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="4" t="n">
         <v>27.09</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>RUA D</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr"/>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>47630000</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>293015</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>293015405000018P</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H107" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" t="n">
+      <c r="I107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="3" t="n">
         <v>26.83</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>RUA MANGUEIRA</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>44270000</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>293170</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>293170715000001P</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H108" s="3" t="inlineStr">
         <is>
           <t>ambiguo</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" t="n">
+      <c r="I108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="3" t="n">
         <v>20.77</v>
       </c>
     </row>
